--- a/BOM/GTV3_Board/Client_BOM.xlsx
+++ b/BOM/GTV3_Board/Client_BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528739A5-6613-4E77-96AB-A7C4570B0438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="419">
   <si>
     <t>Component list</t>
   </si>
@@ -56,9 +55,6 @@
     <t>C1, C4, C17, C21, C23, C24, C31, C43, C58, C61, C63, C65, C67</t>
   </si>
   <si>
-    <t>C2, C6, C10, C15, C18, C22, C25, C26, C27, C28, C29, C30, C33, C36, C37, C38, C39, C40, C41, C44, C46, C47, C48, C49, C51, C52, C55, C57, C60, C62, C64, C66, C68, C69, C73, C76</t>
-  </si>
-  <si>
     <t>C3, C8, C11, C14, C19, C45, C59</t>
   </si>
   <si>
@@ -80,9 +76,6 @@
     <t>C42</t>
   </si>
   <si>
-    <t>C50, C54</t>
-  </si>
-  <si>
     <t>C53, C78</t>
   </si>
   <si>
@@ -356,9 +349,6 @@
     <t>Capacitor 10NF 25V 0603 SMD X7R (reel)</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 100V X7R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 20PF 50V C0G/NPO 0603</t>
   </si>
   <si>
@@ -746,9 +736,6 @@
     <t>CC0603KRX7R8BB103</t>
   </si>
   <si>
-    <t>CC0603KRX7R0BB104</t>
-  </si>
-  <si>
     <t>CC0603JRNPO9BN200</t>
   </si>
   <si>
@@ -1241,21 +1228,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>RVT1E100M0405.</t>
-  </si>
-  <si>
     <t>VT1H471MI135000CE0</t>
   </si>
   <si>
     <t>SS24A</t>
   </si>
   <si>
-    <t>PMEG045V100EPD</t>
-  </si>
-  <si>
     <t>DW254W-11-04-85</t>
   </si>
   <si>
@@ -1265,9 +1243,6 @@
     <t>RU6085H</t>
   </si>
   <si>
-    <t>9C-8.000MEEJ-T</t>
-  </si>
-  <si>
     <t xml:space="preserve"> (GTV3)</t>
   </si>
   <si>
@@ -1292,17 +1267,35 @@
     <t>Bill of Materials for Project (GTV3)</t>
   </si>
   <si>
-    <t>R4, R6, R9, R27, R42, R43, R44, R45, R46, R47, R48, R49, R52, R54, R55, R56, R63, R68, R69, R70, R72, R73, R74, R75, R86, R87, R88, R101, R102, R103, R104, R106, R82</t>
+    <t>C2, C6, C10, C15, C18, C22, C25, C26, C27, C28, C29, C30, C33, C36, C37, C38, C39, C40, C41, C44, C46, C47, C48, C49, C50, C51, C52, C54, C55, C57, C60, C62, C64, C66, C68, C69, C73, C76</t>
+  </si>
+  <si>
+    <t>R4, R6, R9, R27, R42, R43, R44, R45, R46, R47, R48, R49, R52, R54, R55, R56, R63, R68, R69, R70, R72, R73, R74, R75, R82, R86, R87, R88, R101, R102, R103, R104, R106</t>
+  </si>
+  <si>
+    <t>PMEG045V100EPDZ</t>
+  </si>
+  <si>
+    <t>XC32M4-8.000-F18LJDT</t>
+  </si>
+  <si>
+    <t>Merged C50 and C54 due to same parameters</t>
+  </si>
+  <si>
+    <t>RVT1E100M0405</t>
+  </si>
+  <si>
+    <t>R82 merged here due to same parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1429,6 +1422,13 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1689,7 +1689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1860,6 +1860,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2200,25 +2203,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2232,7 +2235,7 @@
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
     </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2241,7 +2244,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2250,7 +2253,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="43"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2259,7 +2262,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2268,7 +2271,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="62"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2277,7 +2280,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2286,7 +2289,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="63"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2304,7 +2307,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="63"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2318,7 +2321,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="63"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2332,7 +2335,7 @@
       <c r="K7" s="7"/>
       <c r="L7" s="63"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2346,68 +2349,68 @@
       <c r="K8" s="7"/>
       <c r="L8" s="63"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J10" s="37">
         <v>13</v>
@@ -2418,68 +2421,70 @@
       </c>
       <c r="L10" s="41"/>
     </row>
-    <row r="11" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B100" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B99" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>8</v>
+        <v>412</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F11" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="J11" s="39">
+        <v>38</v>
+      </c>
+      <c r="K11" s="39">
+        <f t="shared" ref="K11:K73" si="1">J11*5</f>
         <v>190</v>
       </c>
-      <c r="G11" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="J11" s="39">
-        <v>36</v>
-      </c>
-      <c r="K11" s="39">
-        <f t="shared" ref="K11:K74" si="1">J11*5</f>
-        <v>180</v>
-      </c>
-      <c r="L11" s="42"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="64" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J12" s="37">
         <v>7</v>
@@ -2490,32 +2495,32 @@
       </c>
       <c r="L12" s="41"/>
     </row>
-    <row r="13" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J13" s="39">
         <v>5</v>
@@ -2526,32 +2531,32 @@
       </c>
       <c r="L13" s="42"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J14" s="37">
         <v>1</v>
@@ -2562,32 +2567,32 @@
       </c>
       <c r="L14" s="41"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J15" s="39">
         <v>1</v>
@@ -2598,32 +2603,32 @@
       </c>
       <c r="L15" s="42"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J16" s="37">
         <v>1</v>
@@ -2634,32 +2639,32 @@
       </c>
       <c r="L16" s="41"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J17" s="39">
         <v>4</v>
@@ -2670,32 +2675,32 @@
       </c>
       <c r="L17" s="42"/>
     </row>
-    <row r="18" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J18" s="37">
         <v>1</v>
@@ -2706,3023 +2711,2992 @@
       </c>
       <c r="L18" s="41"/>
     </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="J19" s="39">
+      <c r="C19" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="J19" s="37">
         <v>2</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L19" s="42"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="41"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="59" t="s">
-        <v>387</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H20" s="37" t="s">
+      <c r="C20" s="60" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="H20" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="I20" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="J20" s="37">
-        <v>2</v>
-      </c>
-      <c r="K20" s="37">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L20" s="41"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="J20" s="39">
+        <v>1</v>
+      </c>
+      <c r="K20" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L20" s="42"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>347</v>
-      </c>
-      <c r="J21" s="39">
+      <c r="C21" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="J21" s="37">
         <v>1</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="42"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="41"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="59" t="s">
-        <v>387</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="I22" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="J22" s="37">
+      <c r="C22" s="60" t="s">
+        <v>383</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="J22" s="39">
         <v>1</v>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="41"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="42"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I23" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="J23" s="39">
+      <c r="C23" s="59" t="s">
+        <v>383</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="J23" s="37">
         <v>1</v>
       </c>
-      <c r="K23" s="39">
+      <c r="K23" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L23" s="42"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="41"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
-        <f>ROW(B24) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="59" t="s">
-        <v>387</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="I24" s="38" t="s">
-        <v>350</v>
-      </c>
-      <c r="J24" s="37">
+      <c r="C24" s="60" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I24" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="J24" s="39">
         <v>1</v>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L24" s="41"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="42"/>
+    </row>
+    <row r="25" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="F25" s="39" t="s">
+      <c r="C25" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>351</v>
-      </c>
-      <c r="J25" s="39">
+      <c r="G25" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J25" s="37">
         <v>1</v>
       </c>
-      <c r="K25" s="39">
+      <c r="K25" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L25" s="42"/>
-    </row>
-    <row r="26" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="59" t="s">
-        <v>388</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>299</v>
-      </c>
-      <c r="I26" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J26" s="37">
+      <c r="C26" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="H26" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J26" s="39">
         <v>1</v>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L26" s="41"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="42"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="60" t="s">
-        <v>388</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>193</v>
-      </c>
-      <c r="G27" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J27" s="39">
+      <c r="C27" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J27" s="37">
         <v>1</v>
       </c>
-      <c r="K27" s="39">
+      <c r="K27" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L27" s="42"/>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="41"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
-        <v>388</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="I28" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J28" s="37">
-        <v>1</v>
-      </c>
-      <c r="K28" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L28" s="41"/>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="H28" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I28" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J28" s="39">
+        <v>2</v>
+      </c>
+      <c r="K28" s="39">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L28" s="42"/>
+    </row>
+    <row r="29" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="60" t="s">
-        <v>388</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>407</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="I29" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J29" s="39">
-        <v>2</v>
-      </c>
-      <c r="K29" s="39">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L29" s="42"/>
-    </row>
-    <row r="30" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J29" s="37">
+        <v>1</v>
+      </c>
+      <c r="K29" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L29" s="41"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="59" t="s">
-        <v>388</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="H30" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="I30" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J30" s="37">
+      <c r="C30" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>299</v>
+      </c>
+      <c r="I30" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J30" s="39">
         <v>1</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L30" s="41"/>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="42"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>388</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="I31" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J31" s="39">
+      <c r="C31" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J31" s="37">
         <v>1</v>
       </c>
-      <c r="K31" s="39">
+      <c r="K31" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L31" s="42"/>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="41"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="I32" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J32" s="37">
-        <v>1</v>
-      </c>
-      <c r="K32" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L32" s="41"/>
-    </row>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="I32" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J32" s="39">
+        <v>9</v>
+      </c>
+      <c r="K32" s="39">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L32" s="42"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="60" t="s">
-        <v>392</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J33" s="39">
-        <v>9</v>
-      </c>
-      <c r="K33" s="39">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="L33" s="42"/>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="59" t="s">
+        <v>388</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J33" s="37">
+        <v>5</v>
+      </c>
+      <c r="K33" s="37">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="L33" s="41"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>392</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J34" s="37">
+      <c r="C34" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>398</v>
+      </c>
+      <c r="J34" s="39">
+        <v>1</v>
+      </c>
+      <c r="K34" s="39">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K34" s="37">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L34" s="41"/>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L34" s="42"/>
+    </row>
+    <row r="35" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="60" t="s">
-        <v>392</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="I35" s="58" t="s">
-        <v>403</v>
-      </c>
-      <c r="J35" s="39">
+      <c r="C35" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="I35" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J35" s="37">
         <v>1</v>
       </c>
-      <c r="K35" s="39">
+      <c r="K35" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L35" s="42"/>
-    </row>
-    <row r="36" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="41"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
-        <f>ROW(B36) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G36" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="I36" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J36" s="37">
+      <c r="C36" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>401</v>
+      </c>
+      <c r="H36" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J36" s="39">
         <v>1</v>
       </c>
-      <c r="K36" s="37">
+      <c r="K36" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="41"/>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="42"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="60" t="s">
-        <v>390</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>408</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>307</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J37" s="39">
+      <c r="C37" s="59" t="s">
+        <v>385</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="I37" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J37" s="37">
         <v>1</v>
       </c>
-      <c r="K37" s="39">
+      <c r="K37" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="42"/>
-    </row>
-    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L37" s="41"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
-        <f>ROW(B38) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="I38" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J38" s="37">
+      <c r="C38" s="60" t="s">
+        <v>387</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="G38" s="40" t="s">
+        <v>407</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="I38" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="J38" s="39">
         <v>1</v>
       </c>
-      <c r="K38" s="37">
+      <c r="K38" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="41"/>
-    </row>
-    <row r="39" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="42"/>
+    </row>
+    <row r="39" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="60" t="s">
-        <v>391</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>415</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="I39" s="40" t="s">
-        <v>352</v>
-      </c>
-      <c r="J39" s="39">
+      <c r="C39" s="59" t="s">
+        <v>387</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="I39" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="J39" s="37">
         <v>1</v>
       </c>
-      <c r="K39" s="39">
+      <c r="K39" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L39" s="42"/>
-    </row>
-    <row r="40" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L39" s="41"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="59" t="s">
-        <v>391</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="I40" s="38" t="s">
-        <v>353</v>
-      </c>
-      <c r="J40" s="37">
+      <c r="C40" s="60" t="s">
+        <v>387</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="G40" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="H40" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="I40" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="J40" s="39">
         <v>1</v>
       </c>
-      <c r="K40" s="37">
+      <c r="K40" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L40" s="41"/>
-    </row>
-    <row r="41" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L40" s="42"/>
+    </row>
+    <row r="41" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="60" t="s">
-        <v>391</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="40" t="s">
-        <v>248</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>354</v>
-      </c>
-      <c r="J41" s="39">
+      <c r="C41" s="59" t="s">
+        <v>387</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="I41" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="J41" s="37">
         <v>1</v>
       </c>
-      <c r="K41" s="39">
+      <c r="K41" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="42"/>
-    </row>
-    <row r="42" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="41"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
-        <f>ROW(B42) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="59" t="s">
-        <v>391</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="I42" s="38" t="s">
-        <v>355</v>
-      </c>
-      <c r="J42" s="37">
-        <v>1</v>
-      </c>
-      <c r="K42" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L42" s="41"/>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="60" t="s">
+        <v>389</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="G42" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="I42" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J42" s="39">
+        <v>7</v>
+      </c>
+      <c r="K42" s="39">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L42" s="42"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="60" t="s">
-        <v>393</v>
-      </c>
-      <c r="D43" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="G43" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="I43" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J43" s="39">
-        <v>7</v>
-      </c>
-      <c r="K43" s="39">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="L43" s="42"/>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="59" t="s">
+        <v>389</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J43" s="37">
+        <v>1</v>
+      </c>
+      <c r="K43" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L43" s="41"/>
+    </row>
+    <row r="44" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="59" t="s">
-        <v>393</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G44" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="I44" s="38" t="s">
+      <c r="C44" s="60" t="s">
+        <v>390</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G44" s="39" t="s">
         <v>402</v>
       </c>
-      <c r="J44" s="37">
+      <c r="H44" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="I44" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J44" s="39">
         <v>1</v>
       </c>
-      <c r="K44" s="37">
+      <c r="K44" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L44" s="41"/>
-    </row>
-    <row r="45" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L44" s="42"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="60" t="s">
-        <v>394</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="H45" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="I45" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J45" s="39">
+      <c r="C45" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="D45" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J45" s="37">
         <v>1</v>
       </c>
-      <c r="K45" s="39">
+      <c r="K45" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L45" s="42"/>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L45" s="41" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="59" t="s">
-        <v>356</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="I46" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J46" s="37">
-        <v>1</v>
-      </c>
-      <c r="K46" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L46" s="41" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="G46" s="40">
+        <v>61300311121</v>
+      </c>
+      <c r="H46" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J46" s="39">
+        <v>2</v>
+      </c>
+      <c r="K46" s="39">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L46" s="42"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="60" t="s">
-        <v>390</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="G47" s="40">
-        <v>61300311121</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I47" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J47" s="39">
-        <v>2</v>
-      </c>
-      <c r="K47" s="39">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L47" s="42"/>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D47" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="G47" s="38">
+        <v>61300611121</v>
+      </c>
+      <c r="H47" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J47" s="37">
+        <v>4</v>
+      </c>
+      <c r="K47" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L47" s="41"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
-        <f>ROW(B48) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="59" t="s">
-        <v>390</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="G48" s="38">
-        <v>61300611121</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="I48" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J48" s="37">
-        <v>4</v>
-      </c>
-      <c r="K48" s="37">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L48" s="41"/>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D48" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="G48" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J48" s="39">
+        <v>1</v>
+      </c>
+      <c r="K48" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L48" s="42"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="60" t="s">
-        <v>390</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="H49" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="I49" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J49" s="39">
-        <v>1</v>
-      </c>
-      <c r="K49" s="39">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L49" s="42"/>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="G49" s="38">
+        <v>61300211121</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J49" s="37">
+        <v>3</v>
+      </c>
+      <c r="K49" s="37">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L49" s="41"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
-        <f>ROW(B50) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="59" t="s">
-        <v>390</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E50" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="G50" s="38">
-        <v>61300211121</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="I50" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J50" s="37">
-        <v>3</v>
-      </c>
-      <c r="K50" s="37">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L50" s="41"/>
-    </row>
-    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="G50" s="40">
+        <v>61300411121</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="I50" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J50" s="39">
+        <v>1</v>
+      </c>
+      <c r="K50" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L50" s="42"/>
+    </row>
+    <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="60" t="s">
-        <v>390</v>
-      </c>
-      <c r="D51" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E51" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="F51" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="G51" s="40">
-        <v>61300411121</v>
-      </c>
-      <c r="H51" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="I51" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J51" s="39">
-        <v>1</v>
-      </c>
-      <c r="K51" s="39">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L51" s="42"/>
-    </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="D51" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="I51" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J51" s="37">
+        <v>9</v>
+      </c>
+      <c r="K51" s="37">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L51" s="41"/>
+    </row>
+    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
-        <f>ROW(B52) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="G52" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="I52" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J52" s="37">
-        <v>9</v>
-      </c>
-      <c r="K52" s="37">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="L52" s="41"/>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="60" t="s">
+        <v>391</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F52" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G52" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="I52" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J52" s="39">
+        <v>1</v>
+      </c>
+      <c r="K52" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L52" s="42"/>
+    </row>
+    <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="60" t="s">
-        <v>395</v>
-      </c>
-      <c r="D53" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="G53" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="H53" s="39" t="s">
-        <v>318</v>
-      </c>
-      <c r="I53" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J53" s="39">
-        <v>1</v>
-      </c>
-      <c r="K53" s="39">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L53" s="42"/>
-    </row>
-    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="I53" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J53" s="37">
+        <v>2</v>
+      </c>
+      <c r="K53" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L53" s="41"/>
+    </row>
+    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
-        <f>ROW(B54) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="G54" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="I54" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J54" s="37">
+      <c r="C54" s="60" t="s">
+        <v>391</v>
+      </c>
+      <c r="D54" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G54" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="H54" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="I54" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J54" s="39">
         <v>2</v>
       </c>
-      <c r="K54" s="37">
+      <c r="K54" s="39">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L54" s="41"/>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L54" s="42"/>
+    </row>
+    <row r="55" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="60" t="s">
-        <v>395</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="F55" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="G55" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="H55" s="39" t="s">
-        <v>318</v>
-      </c>
-      <c r="I55" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J55" s="39">
-        <v>2</v>
-      </c>
-      <c r="K55" s="39">
-        <f t="shared" si="1"/>
+      <c r="C55" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="G55" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="H55" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I55" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J55" s="37">
         <v>10</v>
       </c>
-      <c r="L55" s="42"/>
-    </row>
-    <row r="56" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K55" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="L55" s="41"/>
+    </row>
+    <row r="56" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
-        <f>ROW(B56) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E56" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="I56" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J56" s="37">
+      <c r="C56" s="60" t="s">
+        <v>391</v>
+      </c>
+      <c r="D56" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="F56" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G56" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="H56" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="I56" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J56" s="39">
+        <v>2</v>
+      </c>
+      <c r="K56" s="39">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K56" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="L56" s="41"/>
-    </row>
-    <row r="57" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L56" s="42"/>
+    </row>
+    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="60" t="s">
-        <v>395</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="E57" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="F57" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="G57" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="H57" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="I57" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J57" s="39">
-        <v>2</v>
-      </c>
-      <c r="K57" s="39">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L57" s="42"/>
-    </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="I57" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J57" s="37">
+        <v>1</v>
+      </c>
+      <c r="K57" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L57" s="41"/>
+    </row>
+    <row r="58" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
-        <f>ROW(B58) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="59" t="s">
-        <v>395</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="E58" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="G58" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="I58" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J58" s="37">
+      <c r="C58" s="60" t="s">
+        <v>391</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="F58" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G58" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="H58" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="I58" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J58" s="39">
         <v>1</v>
       </c>
-      <c r="K58" s="37">
+      <c r="K58" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L58" s="41"/>
-    </row>
-    <row r="59" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L58" s="42"/>
+    </row>
+    <row r="59" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="60" t="s">
-        <v>395</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="E59" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="F59" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G59" s="39" t="s">
-        <v>410</v>
-      </c>
-      <c r="H59" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="I59" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J59" s="39">
+      <c r="C59" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I59" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="J59" s="37">
         <v>1</v>
       </c>
-      <c r="K59" s="39">
+      <c r="K59" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L59" s="42"/>
-    </row>
-    <row r="60" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L59" s="41"/>
+    </row>
+    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f>ROW(B60) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E60" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I60" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="J60" s="37">
+      <c r="C60" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G60" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I60" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="J60" s="39">
         <v>1</v>
       </c>
-      <c r="K60" s="37">
+      <c r="K60" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L60" s="41"/>
-    </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L60" s="42"/>
+    </row>
+    <row r="61" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D61" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E61" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="F61" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G61" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="H61" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I61" s="40" t="s">
-        <v>358</v>
-      </c>
-      <c r="J61" s="39">
+      <c r="C61" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G61" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="I61" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="J61" s="37">
         <v>1</v>
       </c>
-      <c r="K61" s="39">
+      <c r="K61" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L61" s="42"/>
-    </row>
-    <row r="62" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L61" s="41"/>
+    </row>
+    <row r="62" spans="1:12" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <f>ROW(B62) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E62" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="H62" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="I62" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="J62" s="37">
-        <v>1</v>
-      </c>
-      <c r="K62" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L62" s="41"/>
-    </row>
-    <row r="63" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D62" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="E62" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G62" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I62" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="J62" s="39">
+        <v>33</v>
+      </c>
+      <c r="K62" s="39">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+      <c r="L62" s="64" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D63" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="E63" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="F63" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="H63" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I63" s="40" t="s">
-        <v>360</v>
-      </c>
-      <c r="J63" s="39">
-        <v>33</v>
-      </c>
-      <c r="K63" s="39">
-        <f t="shared" si="1"/>
-        <v>165</v>
-      </c>
-      <c r="L63" s="42"/>
-    </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G63" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I63" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="J63" s="37">
+        <v>7</v>
+      </c>
+      <c r="K63" s="37">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L63" s="41"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <f>ROW(B64) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I64" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="J64" s="37">
-        <v>7</v>
-      </c>
-      <c r="K64" s="37">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="L64" s="41"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D64" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G64" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I64" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="J64" s="39">
+        <v>2</v>
+      </c>
+      <c r="K64" s="39">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L64" s="42"/>
+    </row>
+    <row r="65" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D65" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="F65" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G65" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="H65" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I65" s="40" t="s">
-        <v>362</v>
-      </c>
-      <c r="J65" s="39">
-        <v>2</v>
-      </c>
-      <c r="K65" s="39">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L65" s="42"/>
-    </row>
-    <row r="66" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="H65" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="I65" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="J65" s="37">
+        <v>1</v>
+      </c>
+      <c r="K65" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L65" s="41"/>
+    </row>
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
-        <f>ROW(B66) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D66" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="I66" s="38" t="s">
-        <v>363</v>
-      </c>
-      <c r="J66" s="37">
+      <c r="C66" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D66" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="F66" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G66" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="H66" s="39" t="s">
+        <v>320</v>
+      </c>
+      <c r="I66" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="J66" s="39">
         <v>1</v>
       </c>
-      <c r="K66" s="37">
+      <c r="K66" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L66" s="41"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L66" s="42"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D67" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="F67" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G67" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="H67" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="I67" s="40" t="s">
-        <v>364</v>
-      </c>
-      <c r="J67" s="39">
-        <v>1</v>
-      </c>
-      <c r="K67" s="39">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L67" s="42"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G67" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="I67" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="J67" s="37">
+        <v>8</v>
+      </c>
+      <c r="K67" s="37">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L67" s="41"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
-        <f>ROW(B68) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E68" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G68" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="I68" s="38" t="s">
-        <v>365</v>
-      </c>
-      <c r="J68" s="37">
-        <v>8</v>
-      </c>
-      <c r="K68" s="37">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L68" s="41"/>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D68" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="F68" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G68" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="H68" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I68" s="40" t="s">
+        <v>362</v>
+      </c>
+      <c r="J68" s="39">
+        <v>3</v>
+      </c>
+      <c r="K68" s="39">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L68" s="42"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D69" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="F69" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G69" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="H69" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I69" s="40" t="s">
-        <v>366</v>
-      </c>
-      <c r="J69" s="39">
-        <v>3</v>
-      </c>
-      <c r="K69" s="39">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L69" s="42"/>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G69" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="I69" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="J69" s="37">
+        <v>7</v>
+      </c>
+      <c r="K69" s="37">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L69" s="41"/>
+    </row>
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
-        <f>ROW(B70) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E70" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G70" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="I70" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="J70" s="37">
-        <v>7</v>
-      </c>
-      <c r="K70" s="37">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="L70" s="41"/>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="F70" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G70" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H70" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I70" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="J70" s="39">
+        <v>2</v>
+      </c>
+      <c r="K70" s="39">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L70" s="42"/>
+    </row>
+    <row r="71" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D71" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="F71" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G71" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="H71" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I71" s="40" t="s">
-        <v>368</v>
-      </c>
-      <c r="J71" s="39">
-        <v>2</v>
-      </c>
-      <c r="K71" s="39">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L71" s="42"/>
-    </row>
-    <row r="72" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E71" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I71" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="J71" s="37">
+        <v>13</v>
+      </c>
+      <c r="K71" s="37">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="L71" s="41"/>
+    </row>
+    <row r="72" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
-        <f>ROW(B72) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G72" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I72" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="J72" s="37">
-        <v>13</v>
-      </c>
-      <c r="K72" s="37">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="L72" s="41"/>
-    </row>
-    <row r="73" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D72" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="F72" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G72" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="H72" s="39" t="s">
+        <v>322</v>
+      </c>
+      <c r="I72" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="J72" s="39">
+        <v>1</v>
+      </c>
+      <c r="K72" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L72" s="42"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D73" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E73" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="F73" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G73" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="H73" s="39" t="s">
-        <v>326</v>
-      </c>
-      <c r="I73" s="40" t="s">
-        <v>370</v>
-      </c>
-      <c r="J73" s="39">
+      <c r="C73" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E73" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G73" s="38" t="s">
+        <v>409</v>
+      </c>
+      <c r="H73" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I73" s="38" t="s">
+        <v>406</v>
+      </c>
+      <c r="J73" s="37">
         <v>1</v>
       </c>
-      <c r="K73" s="39">
+      <c r="K73" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L73" s="42"/>
-    </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L73" s="41"/>
+    </row>
+    <row r="74" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
-        <f>ROW(B74) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E74" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G74" s="38" t="s">
-        <v>417</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I74" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="J74" s="37">
+      <c r="C74" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D74" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F74" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G74" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="H74" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I74" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="J74" s="39">
         <v>1</v>
       </c>
-      <c r="K74" s="37">
-        <f t="shared" si="1"/>
+      <c r="K74" s="39">
+        <f t="shared" ref="K74:K100" si="2">J74*5</f>
         <v>5</v>
       </c>
-      <c r="L74" s="41"/>
-    </row>
-    <row r="75" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L74" s="42"/>
+    </row>
+    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D75" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E75" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="F75" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G75" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="H75" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I75" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="J75" s="39">
-        <v>1</v>
-      </c>
-      <c r="K75" s="39">
-        <f t="shared" ref="K75:K101" si="2">J75*5</f>
-        <v>5</v>
-      </c>
-      <c r="L75" s="42"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E75" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G75" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I75" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="J75" s="37">
+        <v>2</v>
+      </c>
+      <c r="K75" s="37">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="L75" s="41"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f>ROW(B76) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E76" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I76" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="J76" s="37">
-        <v>2</v>
-      </c>
-      <c r="K76" s="37">
+      <c r="C76" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G76" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="H76" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I76" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="J76" s="39">
+        <v>4</v>
+      </c>
+      <c r="K76" s="39">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="L76" s="41"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L76" s="42"/>
+    </row>
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D77" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E77" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="F77" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G77" s="40" t="s">
-        <v>275</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I77" s="40" t="s">
-        <v>373</v>
-      </c>
-      <c r="J77" s="39">
-        <v>4</v>
-      </c>
-      <c r="K77" s="39">
+      <c r="C77" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E77" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F77" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="G77" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="I77" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="J77" s="37">
+        <v>1</v>
+      </c>
+      <c r="K77" s="37">
         <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L77" s="42"/>
-    </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="L77" s="41"/>
+    </row>
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <f>ROW(B78) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="E78" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="G78" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="I78" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="J78" s="37">
+      <c r="C78" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D78" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F78" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G78" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I78" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="J78" s="39">
         <v>1</v>
       </c>
-      <c r="K78" s="37">
+      <c r="K78" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L78" s="41"/>
-    </row>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L78" s="42"/>
+    </row>
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D79" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E79" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F79" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G79" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="H79" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I79" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="J79" s="39">
-        <v>1</v>
-      </c>
-      <c r="K79" s="39">
+      <c r="C79" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E79" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G79" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="I79" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="J79" s="37">
+        <v>3</v>
+      </c>
+      <c r="K79" s="37">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L79" s="42"/>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L79" s="41"/>
+    </row>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
       <c r="C80" s="59" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E80" s="38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I80" s="38" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J80" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K80" s="37">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L80" s="41"/>
     </row>
-    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f>ROW(B81) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D81" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="E81" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G81" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="H81" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I81" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="J81" s="37">
+      <c r="C81" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D81" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="E81" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="F81" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G81" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="H81" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I81" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="J81" s="39">
         <v>2</v>
       </c>
-      <c r="K81" s="37">
+      <c r="K81" s="39">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L81" s="41"/>
-    </row>
-    <row r="82" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L81" s="42"/>
+    </row>
+    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="D82" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E82" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F82" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G82" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="H82" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I82" s="40" t="s">
-        <v>378</v>
-      </c>
-      <c r="J82" s="39">
+      <c r="C82" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D82" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="G82" s="38" t="s">
+        <v>410</v>
+      </c>
+      <c r="H82" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="I82" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="J82" s="37">
         <v>2</v>
       </c>
-      <c r="K82" s="39">
+      <c r="K82" s="37">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L82" s="42"/>
-    </row>
-    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L82" s="41"/>
+    </row>
+    <row r="83" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f>ROW(B83) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D83" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E83" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="G83" s="38" t="s">
-        <v>418</v>
-      </c>
-      <c r="H83" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="I83" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="J83" s="37">
+      <c r="C83" s="60" t="s">
+        <v>392</v>
+      </c>
+      <c r="D83" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E83" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="F83" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G83" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="H83" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="I83" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="J83" s="39">
         <v>2</v>
       </c>
-      <c r="K83" s="37">
+      <c r="K83" s="39">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L83" s="41"/>
-    </row>
-    <row r="84" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L83" s="42"/>
+    </row>
+    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
+        <f>ROW(B84) - ROW($B$9)</f>
+        <v>75</v>
+      </c>
+      <c r="C84" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="D84" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="F84" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G84" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="H84" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="I84" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="J84" s="37">
+        <v>1</v>
+      </c>
+      <c r="K84" s="37">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L84" s="41"/>
+    </row>
+    <row r="85" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="53">
         <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="C84" s="60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="D85" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E85" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F85" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="D84" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E84" s="40" t="s">
+      <c r="G85" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="H85" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="I85" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J85" s="39">
+        <v>18</v>
+      </c>
+      <c r="K85" s="39">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="L85" s="42"/>
+    </row>
+    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="1"/>
+      <c r="B86" s="53">
+        <f>ROW(B86) - ROW($B$9)</f>
+        <v>77</v>
+      </c>
+      <c r="C86" s="59" t="s">
+        <v>393</v>
+      </c>
+      <c r="D86" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="E86" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="F84" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="G84" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="H84" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="I84" s="40" t="s">
-        <v>380</v>
-      </c>
-      <c r="J84" s="39">
+      <c r="F86" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G86" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="H86" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="I86" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J86" s="37">
+        <v>7</v>
+      </c>
+      <c r="K86" s="37">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="L86" s="41"/>
+    </row>
+    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="53">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C87" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G87" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="H87" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="I87" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J87" s="39">
         <v>2</v>
       </c>
-      <c r="K84" s="39">
+      <c r="K87" s="39">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L84" s="42"/>
-    </row>
-    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-      <c r="B85" s="53">
-        <f>ROW(B85) - ROW($B$9)</f>
-        <v>76</v>
-      </c>
-      <c r="C85" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E85" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="F85" s="37" t="s">
+      <c r="L87" s="42"/>
+    </row>
+    <row r="88" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="B88" s="53">
+        <f>ROW(B88) - ROW($B$9)</f>
+        <v>79</v>
+      </c>
+      <c r="C88" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="D88" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="F88" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="G85" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="I85" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="J85" s="37">
+      <c r="G88" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="H88" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="I88" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J88" s="37">
         <v>1</v>
       </c>
-      <c r="K85" s="37">
+      <c r="K88" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L85" s="41"/>
-    </row>
-    <row r="86" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="1"/>
-      <c r="B86" s="53">
-        <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="C86" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="D86" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E86" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="F86" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G86" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="H86" s="39" t="s">
-        <v>402</v>
-      </c>
-      <c r="I86" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J86" s="39">
-        <v>18</v>
-      </c>
-      <c r="K86" s="39">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="L86" s="42"/>
-    </row>
-    <row r="87" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1"/>
-      <c r="B87" s="53">
-        <f>ROW(B87) - ROW($B$9)</f>
-        <v>78</v>
-      </c>
-      <c r="C87" s="59" t="s">
-        <v>397</v>
-      </c>
-      <c r="D87" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E87" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G87" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="I87" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J87" s="37">
-        <v>7</v>
-      </c>
-      <c r="K87" s="37">
-        <f t="shared" si="2"/>
-        <v>35</v>
-      </c>
-      <c r="L87" s="41"/>
-    </row>
-    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="53">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="C88" s="60" t="s">
-        <v>398</v>
-      </c>
-      <c r="D88" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E88" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F88" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="H88" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="I88" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J88" s="39">
-        <v>2</v>
-      </c>
-      <c r="K88" s="39">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="L88" s="42"/>
-    </row>
-    <row r="89" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L88" s="41"/>
+    </row>
+    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
-        <f>ROW(B89) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="59" t="s">
+      <c r="C89" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F89" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="H89" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="I89" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D89" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E89" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="F89" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="G89" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="H89" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="I89" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J89" s="37">
+      <c r="J89" s="39">
         <v>1</v>
       </c>
-      <c r="K89" s="37">
+      <c r="K89" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L89" s="41"/>
-    </row>
-    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L89" s="42"/>
+    </row>
+    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="C90" s="60" t="s">
+      <c r="C90" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="D90" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="F90" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G90" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="H90" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="I90" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="D90" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="F90" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="G90" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="H90" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="I90" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J90" s="39">
+      <c r="J90" s="37">
         <v>1</v>
       </c>
-      <c r="K90" s="39">
+      <c r="K90" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L90" s="42"/>
-    </row>
-    <row r="91" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L90" s="41"/>
+    </row>
+    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="53">
-        <f>ROW(B91) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="59" t="s">
+      <c r="C91" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="F91" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G91" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="H91" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="I91" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D91" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="E91" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="G91" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="H91" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="I91" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J91" s="37">
+      <c r="J91" s="39">
         <v>1</v>
       </c>
-      <c r="K91" s="37">
+      <c r="K91" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L91" s="41"/>
-    </row>
-    <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L91" s="42"/>
+    </row>
+    <row r="92" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="60" t="s">
+      <c r="C92" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="F92" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="H92" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="I92" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="D92" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="E92" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="F92" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="G92" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="H92" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I92" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J92" s="39">
+      <c r="J92" s="37">
         <v>1</v>
       </c>
-      <c r="K92" s="39">
+      <c r="K92" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L92" s="42"/>
-    </row>
-    <row r="93" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L92" s="41"/>
+    </row>
+    <row r="93" spans="1:12" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="53">
-        <f>ROW(B93) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="59" t="s">
+      <c r="C93" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D93" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E93" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="F93" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G93" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="H93" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="I93" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D93" s="37" t="s">
+      <c r="J93" s="39">
+        <v>4</v>
+      </c>
+      <c r="K93" s="39">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="L93" s="42"/>
+    </row>
+    <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="1"/>
+      <c r="B94" s="53">
+        <f>ROW(B94) - ROW($B$9)</f>
+        <v>85</v>
+      </c>
+      <c r="C94" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="D94" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="E93" s="38" t="s">
+      <c r="E94" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="F94" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="G94" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="H94" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="I94" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J94" s="37">
+        <v>3</v>
+      </c>
+      <c r="K94" s="37">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="L94" s="41"/>
+    </row>
+    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="1"/>
+      <c r="B95" s="53">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C95" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D95" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E95" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="F93" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="G93" s="38" t="s">
+      <c r="F95" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="H93" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="I93" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J93" s="37">
+      <c r="G95" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="H95" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="I95" s="40" t="s">
+        <v>398</v>
+      </c>
+      <c r="J95" s="39">
         <v>1</v>
       </c>
-      <c r="K93" s="37">
+      <c r="K95" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L93" s="41"/>
-    </row>
-    <row r="94" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="B94" s="53">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="C94" s="60" t="s">
-        <v>398</v>
-      </c>
-      <c r="D94" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E94" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="F94" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G94" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="H94" s="39" t="s">
-        <v>334</v>
-      </c>
-      <c r="I94" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J94" s="39">
-        <v>4</v>
-      </c>
-      <c r="K94" s="39">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="L94" s="42"/>
-    </row>
-    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
-      <c r="B95" s="53">
-        <f>ROW(B95) - ROW($B$9)</f>
-        <v>86</v>
-      </c>
-      <c r="C95" s="59" t="s">
-        <v>398</v>
-      </c>
-      <c r="D95" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="E95" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="F95" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="G95" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="H95" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="I95" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J95" s="37">
-        <v>3</v>
-      </c>
-      <c r="K95" s="37">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="L95" s="41"/>
-    </row>
-    <row r="96" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L95" s="42"/>
+    </row>
+    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B96) - ROW($B$9)</f>
         <v>87</v>
       </c>
-      <c r="C96" s="60" t="s">
+      <c r="C96" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="D96" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="F96" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="G96" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="H96" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="I96" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="D96" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E96" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="F96" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="G96" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="H96" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="I96" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J96" s="39">
+      <c r="J96" s="37">
         <v>1</v>
       </c>
-      <c r="K96" s="39">
+      <c r="K96" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L96" s="42"/>
-    </row>
-    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L96" s="41"/>
+    </row>
+    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="53">
-        <f>ROW(B97) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="C97" s="59" t="s">
+      <c r="C97" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D97" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E97" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="F97" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G97" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="H97" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="I97" s="40" t="s">
         <v>398</v>
       </c>
-      <c r="D97" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E97" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="F97" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="G97" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="H97" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="I97" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J97" s="37">
+      <c r="J97" s="39">
         <v>1</v>
       </c>
-      <c r="K97" s="37">
+      <c r="K97" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L97" s="41"/>
-    </row>
-    <row r="98" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L97" s="42"/>
+    </row>
+    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B98) - ROW($B$9)</f>
         <v>89</v>
       </c>
-      <c r="C98" s="60" t="s">
+      <c r="C98" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="D98" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E98" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G98" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="H98" s="37" t="s">
         <v>398</v>
       </c>
-      <c r="D98" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="E98" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="F98" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G98" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="H98" s="39" t="s">
-        <v>336</v>
-      </c>
-      <c r="I98" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="J98" s="39">
+      <c r="I98" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="J98" s="37">
         <v>1</v>
       </c>
-      <c r="K98" s="39">
+      <c r="K98" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L98" s="42"/>
-    </row>
-    <row r="99" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L98" s="41"/>
+    </row>
+    <row r="99" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="53">
-        <f>ROW(B99) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="C99" s="59" t="s">
-        <v>399</v>
-      </c>
-      <c r="D99" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E99" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="F99" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G99" s="37" t="s">
-        <v>411</v>
-      </c>
-      <c r="H99" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="I99" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="J99" s="37">
+      <c r="C99" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="D99" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E99" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="F99" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G99" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="H99" s="39" t="s">
+        <v>317</v>
+      </c>
+      <c r="I99" s="40" t="s">
+        <v>377</v>
+      </c>
+      <c r="J99" s="39">
         <v>1</v>
       </c>
-      <c r="K99" s="37">
+      <c r="K99" s="39">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L99" s="41"/>
-    </row>
-    <row r="100" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L99" s="42"/>
+    </row>
+    <row r="100" spans="1:12" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B100) - ROW($B$9)</f>
         <v>91</v>
       </c>
-      <c r="C100" s="60" t="s">
-        <v>399</v>
-      </c>
-      <c r="D100" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E100" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="F100" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="G100" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="H100" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="I100" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="J100" s="39">
+      <c r="C100" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="D100" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E100" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F100" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G100" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="H100" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="I100" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="J100" s="37">
         <v>1</v>
       </c>
-      <c r="K100" s="39">
+      <c r="K100" s="37">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L100" s="42"/>
-    </row>
-    <row r="101" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L100" s="41"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
-      <c r="B101" s="53">
-        <f>ROW(B101) - ROW($B$9)</f>
-        <v>92</v>
-      </c>
-      <c r="C101" s="59" t="s">
-        <v>399</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E101" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="G101" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="H101" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="I101" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="J101" s="37">
-        <v>1</v>
-      </c>
-      <c r="K101" s="37">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L101" s="41"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B101" s="32"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="33"/>
+      <c r="E101" s="34"/>
+      <c r="F101" s="35"/>
+      <c r="G101" s="36"/>
+      <c r="H101" s="35"/>
+      <c r="I101" s="36"/>
+      <c r="J101" s="36"/>
+      <c r="K101" s="36"/>
+      <c r="L101" s="44"/>
+    </row>
+    <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
-      <c r="B102" s="32"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="34"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="36"/>
-      <c r="H102" s="35"/>
-      <c r="I102" s="36"/>
-      <c r="J102" s="36"/>
-      <c r="K102" s="36"/>
-      <c r="L102" s="44"/>
-    </row>
-    <row r="103" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="24"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="45"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
-      <c r="B103" s="24"/>
-      <c r="C103" s="52"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
-      <c r="L103" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
